--- a/next-app/public/OptimIQ_Portal_Screen_Approval_Inventory.xlsx
+++ b/next-app/public/OptimIQ_Portal_Screen_Approval_Inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen Inventory" sheetId="1" r:id="R4803b25c07704b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme &amp; Review" sheetId="2" r:id="R267cefd24641429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen Inventory" sheetId="1" r:id="R150f23b85354435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme &amp; Review" sheetId="2" r:id="R96081ee0edc14075"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -243,7 +243,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R04d73fb0ee294a4b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rece095b6118f4f72"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -495,7 +495,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>Client review tracker — includes four role workspace concepts for review; no screen has client approval yet.</x:v>
+        <x:v>Client review tracker — Theme 1 is approved; the shared sign-in and four role workspaces are tracked for screen-level review.</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -584,12 +584,14 @@
         <x:v>Single entry point for every account type; after authentication, route to authorised workspace and active role.</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Sign-in method, MFA/OTP use, and recovery flow are not defined. Existing website email OTP is verification, not necessarily portal login.</x:v>
+        <x:v>CTA registration performs email verification and password setup; portal sign-in uses those credentials. Account-recovery flow remains open for developer confirmation.</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
         <x:v>Needs clarification</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="str"/>
+      <x:c r="H8" s="12" t="str">
+        <x:v>Sign-in concept created at /login/. Existing CTA registration pages are outside this redesign scope and must not be changed.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="108" hidden="0" customHeight="1">
       <x:c r="A9" s="15" t="str">
@@ -1842,7 +1844,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1506bc6748f4e79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88416a6bc2f94f94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2045,6 +2047,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21943529d2244d16"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86af5b69032942cb"/>
 </x:worksheet>
 </file>